--- a/output/pdf_financials_xlsx/HSTR.xlsx
+++ b/output/pdf_financials_xlsx/HSTR.xlsx
@@ -1338,16 +1338,16 @@
         <v>0.921328</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.326083</v>
+        <v>-2.326083</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.583573</v>
+        <v>-0.583573</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.307007</v>
+        <v>-4.307007</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.163604</v>
+        <v>-1.163604</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-1.594162</v>
@@ -1385,19 +1385,19 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.0196</v>
+        <v>-1.607224</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.010812</v>
+        <v>-3.68936</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.002307</v>
+        <v>-3.965159</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.005828</v>
+        <v>-2.764028</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.8079769999999999</v>
+        <v>-2.650633</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.813412</v>
+        <v>-0.813412</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.850086</v>
+        <v>-1.850086</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.983733</v>
+        <v>-1.983733</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.3791</v>
+        <v>-1.3791</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.729305</v>
+        <v>-1.729305</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.326083</v>
+        <v>-2.326083</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.583573</v>
+        <v>-0.583573</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.307007</v>
+        <v>-4.307007</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.163604</v>
+        <v>-1.163604</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-1.594162</v>
@@ -1817,31 +1817,31 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.813412</v>
+        <v>-0.813412</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.850086</v>
+        <v>-1.850086</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.983733</v>
+        <v>-1.983733</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.3791</v>
+        <v>-1.3791</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.729305</v>
+        <v>-1.729305</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.326083</v>
+        <v>-2.326083</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.583573</v>
+        <v>-0.583573</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4.307007</v>
+        <v>-4.307007</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.163604</v>
+        <v>-1.163604</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.594162</v>
@@ -2116,16 +2116,16 @@
         <v>0.921328</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.326083</v>
+        <v>-2.326083</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.583573</v>
+        <v>-0.583573</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>4.307007</v>
+        <v>-4.307007</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.163604</v>
+        <v>-1.163604</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.594162</v>
@@ -2240,16 +2240,16 @@
         <v>0.921328</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.326083</v>
+        <v>-2.326083</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.583573</v>
+        <v>-0.583573</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4.317966</v>
+        <v>-4.296048</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.169307</v>
+        <v>-1.157901</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.590188</v>
@@ -2377,31 +2377,31 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.469098476717409</v>
+        <v>202.4690984767174</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.587840637120951</v>
+        <v>200.587840637121</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.1164312974595064</v>
+        <v>200.1164312974595</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4208161001871578</v>
+        <v>199.5791838998128</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>87.69699824601011</v>
+        <v>287.6969982460101</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -5999,34 +5999,34 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.101048</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.091078</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.79899</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.296629</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.56961</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.978542</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.237729</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.302</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>9.079000000000001</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="93">
@@ -7576,13 +7576,13 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.718734</v>
+        <v>-7.826444</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.133728</v>
+        <v>-4.573405</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-1.473047</v>
+        <v>0.190368</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -11444,7 +11444,11 @@
           <t>Reserves 13 10,370</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -14965,7 +14969,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -16907,7 +16915,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -17693,7 +17705,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -19473,7 +19489,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -42635,7 +42655,11 @@
           <t>Recoveries of acquisition of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -44522,7 +44546,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -44619,7 +44647,11 @@
           <t>Recoveries of acquisition of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -46326,7 +46358,11 @@
           <t>Acquisition of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -58990,10 +59026,10 @@
         </is>
       </c>
       <c r="N504" s="5" t="n">
-        <v>4.307007</v>
+        <v>-4.307007</v>
       </c>
       <c r="O504" s="5" t="n">
-        <v>1.163604</v>
+        <v>-1.163604</v>
       </c>
       <c r="P504" s="5" t="n">
         <v>-1.594162</v>
@@ -62076,16 +62112,16 @@
         </is>
       </c>
       <c r="M535" s="5" t="n">
-        <v>0.583573</v>
+        <v>-0.583573</v>
       </c>
       <c r="N535" s="5" t="n">
-        <v>4.307007</v>
+        <v>-4.307007</v>
       </c>
       <c r="O535" s="5" t="n">
-        <v>1.163604</v>
+        <v>-1.163604</v>
       </c>
       <c r="P535" s="5" t="n">
-        <v>1.594162</v>
+        <v>-1.594162</v>
       </c>
       <c r="Q535" t="inlineStr">
         <is>
@@ -62385,10 +62421,10 @@
         </is>
       </c>
       <c r="O538" s="5" t="n">
-        <v>4.807683</v>
+        <v>-4.807683</v>
       </c>
       <c r="P538" s="5" t="n">
-        <v>2.040859</v>
+        <v>-2.040859</v>
       </c>
       <c r="Q538" t="inlineStr">
         <is>
@@ -63584,10 +63620,10 @@
         </is>
       </c>
       <c r="N550" s="5" t="n">
-        <v>0.859587</v>
+        <v>-0.859587</v>
       </c>
       <c r="O550" s="5" t="n">
-        <v>4.807683</v>
+        <v>-4.807683</v>
       </c>
       <c r="P550" t="inlineStr">
         <is>
@@ -64488,10 +64524,10 @@
         </is>
       </c>
       <c r="M559" s="5" t="n">
-        <v>0.571597</v>
+        <v>-0.571597</v>
       </c>
       <c r="N559" s="5" t="n">
-        <v>0.859587</v>
+        <v>-0.859587</v>
       </c>
       <c r="O559" t="inlineStr">
         <is>
@@ -65396,10 +65432,10 @@
         </is>
       </c>
       <c r="L568" s="5" t="n">
-        <v>2.326083</v>
+        <v>-2.326083</v>
       </c>
       <c r="M568" s="5" t="n">
-        <v>0.583573</v>
+        <v>-0.583573</v>
       </c>
       <c r="N568" t="inlineStr">
         <is>
@@ -65598,10 +65634,10 @@
         </is>
       </c>
       <c r="L570" s="5" t="n">
-        <v>2.221094</v>
+        <v>-2.221094</v>
       </c>
       <c r="M570" s="5" t="n">
-        <v>0.571597</v>
+        <v>-0.571597</v>
       </c>
       <c r="N570" t="inlineStr">
         <is>
@@ -67698,10 +67734,10 @@
         </is>
       </c>
       <c r="K591" s="5" t="n">
-        <v>1.729305</v>
+        <v>-1.729305</v>
       </c>
       <c r="L591" s="5" t="n">
-        <v>2.326083</v>
+        <v>-2.326083</v>
       </c>
       <c r="M591" t="inlineStr">
         <is>
@@ -67895,13 +67931,13 @@
         </is>
       </c>
       <c r="J593" s="5" t="n">
-        <v>1.347897</v>
+        <v>-1.347897</v>
       </c>
       <c r="K593" s="5" t="n">
-        <v>1.760099</v>
+        <v>-1.760099</v>
       </c>
       <c r="L593" s="5" t="n">
-        <v>2.221094</v>
+        <v>-2.221094</v>
       </c>
       <c r="M593" t="inlineStr">
         <is>
@@ -68905,10 +68941,10 @@
         </is>
       </c>
       <c r="J603" s="5" t="n">
-        <v>1.3791</v>
+        <v>-1.3791</v>
       </c>
       <c r="K603" s="5" t="n">
-        <v>0.919789</v>
+        <v>-0.919789</v>
       </c>
       <c r="L603" t="inlineStr">
         <is>
@@ -71195,10 +71231,10 @@
         </is>
       </c>
       <c r="I626" s="5" t="n">
-        <v>1.983733</v>
+        <v>-1.983733</v>
       </c>
       <c r="J626" s="5" t="n">
-        <v>1.3791</v>
+        <v>-1.3791</v>
       </c>
       <c r="K626" t="inlineStr">
         <is>
@@ -72799,13 +72835,13 @@
         </is>
       </c>
       <c r="G642" s="5" t="n">
-        <v>0.813412</v>
+        <v>-0.813412</v>
       </c>
       <c r="H642" s="5" t="n">
-        <v>1.850086</v>
+        <v>-1.850086</v>
       </c>
       <c r="I642" s="5" t="n">
-        <v>1.983733</v>
+        <v>-1.983733</v>
       </c>
       <c r="J642" t="inlineStr">
         <is>
@@ -73004,10 +73040,10 @@
         </is>
       </c>
       <c r="H644" s="5" t="n">
-        <v>1.925772</v>
+        <v>-1.925772</v>
       </c>
       <c r="I644" s="5" t="n">
-        <v>1.999885</v>
+        <v>-1.999885</v>
       </c>
       <c r="J644" t="inlineStr">
         <is>
@@ -75003,10 +75039,10 @@
         </is>
       </c>
       <c r="G664" s="5" t="n">
-        <v>0.767913</v>
+        <v>-0.767913</v>
       </c>
       <c r="H664" s="5" t="n">
-        <v>1.880273</v>
+        <v>-1.880273</v>
       </c>
       <c r="I664" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HSTR.xlsx
+++ b/output/pdf_financials_xlsx/HSTR.xlsx
@@ -1075,46 +1075,46 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000286</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010121</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000375</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-2e-06</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017317</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00063</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.027976</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013155</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004666</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000118</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.001168</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.001732</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.013693</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.048225</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2101,46 +2101,46 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.793812</v>
+        <v>0.794098</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.839274</v>
+        <v>1.849395</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.981426</v>
+        <v>1.981801</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.384928</v>
+        <v>1.38493</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.921328</v>
+        <v>0.938645</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.326083</v>
+        <v>-2.325453</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.583573</v>
+        <v>-0.555597</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.307007</v>
+        <v>-4.293852</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.163604</v>
+        <v>-1.158938</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.594162</v>
+        <v>-1.59428</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-8.255849</v>
+        <v>-8.257016999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-12.456251</v>
+        <v>-12.457983</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-4.531706</v>
+        <v>-4.545399</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-14.781</v>
+        <v>-14.829225</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>27.483</v>
@@ -2225,46 +2225,46 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.793812</v>
+        <v>0.794098</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.839274</v>
+        <v>1.849395</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.981426</v>
+        <v>1.981801</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.384928</v>
+        <v>1.38493</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.921328</v>
+        <v>0.938645</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.326083</v>
+        <v>-2.325453</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.583573</v>
+        <v>-0.555597</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.296048</v>
+        <v>-4.282893</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.157901</v>
+        <v>-1.153235</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.590188</v>
+        <v>-1.590306</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-8.245888000000001</v>
+        <v>-8.247056000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-12.403453</v>
+        <v>-12.405185</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.502865</v>
+        <v>-4.516558</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-14.663</v>
+        <v>-14.711225</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>29.073</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.021724</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.097562</v>
@@ -2562,19 +2562,19 @@
         <v>0.053992</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.238723</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.183046</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.051</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>27.185</v>
       </c>
     </row>
     <row r="35">
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.01575</v>
+        <v>0.037474</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.9411620000000001</v>
@@ -2678,19 +2678,19 @@
         <v>0.059742</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.02875</v>
+        <v>1.267473</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.02875</v>
+        <v>1.211796</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.02875</v>
+        <v>3.07975</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.02875</v>
+        <v>0.58475</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>27.185</v>
       </c>
     </row>
     <row r="37">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.039453</v>
+        <v>0.017729</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.0317</v>
@@ -3374,10 +3374,10 @@
         <v>1.192983</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.117868</v>
+        <v>1.879145</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.846343</v>
+        <v>0.663297</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.043</v>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -18002,7 +18002,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
@@ -54005,7 +54005,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -58680,7 +58680,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -61480,7 +61480,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -67401,7 +67401,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -70516,7 +70516,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -74324,7 +74324,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">

--- a/output/pdf_financials_xlsx/HSTR.xlsx
+++ b/output/pdf_financials_xlsx/HSTR.xlsx
@@ -1176,10 +1176,10 @@
         <v>-0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>0.193</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>2.033</v>
       </c>
     </row>
     <row r="14">
@@ -2140,10 +2140,10 @@
         <v>-4.545399</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-14.829225</v>
+        <v>-15.022225</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>27.483</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="28">
@@ -2264,10 +2264,10 @@
         <v>-4.516558</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-14.711225</v>
+        <v>-14.904225</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>29.073</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="30">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="R30" s="3" t="n">
-        <v>79.49089517143327</v>
+        <v>73.93230163504128</v>
       </c>
     </row>
     <row r="31">
@@ -49103,7 +49103,11 @@
           <t>Net finance expenses 11</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
